--- a/data/trans_camb/P12_1_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 6,68</t>
+          <t>-3,55; 7,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,7</t>
+          <t>-9,92; -0,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,03</t>
+          <t>-7,2; 2,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 3,85</t>
+          <t>-7,78; 5,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -2,69</t>
+          <t>-13,7; -2,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 2,22</t>
+          <t>-8,2; 2,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,52</t>
+          <t>-3,85; 4,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -2,67</t>
+          <t>-9,82; -2,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,91</t>
+          <t>-5,87; 1,43</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 50,91</t>
+          <t>-20,54; 53,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,89; -3,45</t>
+          <t>-55,3; -3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 16,08</t>
+          <t>-40,13; 16,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 23,49</t>
+          <t>-34,49; 32,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,59; -14,9</t>
+          <t>-59,6; -13,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 14,24</t>
+          <t>-34,84; 15,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 30,28</t>
+          <t>-19,89; 27,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,36; -16,03</t>
+          <t>-51,9; -16,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 6,14</t>
+          <t>-30,49; 10,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 9,2</t>
+          <t>-1,49; 9,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 2,98</t>
+          <t>-6,95; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,31</t>
+          <t>-4,2; 5,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 11,07</t>
+          <t>-1,99; 10,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -1,75</t>
+          <t>-13,17; -2,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 4,64</t>
+          <t>-5,81; 5,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 8,08</t>
+          <t>-0,49; 7,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -1,33</t>
+          <t>-8,49; -1,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 3,48</t>
+          <t>-3,92; 3,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 97,71</t>
+          <t>-10,71; 101,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 31,44</t>
+          <t>-48,71; 26,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 56,85</t>
+          <t>-28,07; 60,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 62,32</t>
+          <t>-9,19; 57,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,59; -9,82</t>
+          <t>-55,78; -12,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 27,35</t>
+          <t>-25,04; 29,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 54,6</t>
+          <t>-2,79; 55,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,48; -7,78</t>
+          <t>-47,06; -10,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 24,34</t>
+          <t>-21,09; 23,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,41</t>
+          <t>-4,88; 3,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; -2,45</t>
+          <t>-11,15; -2,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -1,64</t>
+          <t>-17,5; -1,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 12,4</t>
+          <t>-4,82; 12,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 9,41</t>
+          <t>-10,28; 8,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 5,76</t>
+          <t>-9,41; 5,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 5,16</t>
+          <t>-2,77; 5,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,65; -1,22</t>
+          <t>-9,32; -1,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; -1,25</t>
+          <t>-16,94; -1,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 21,48</t>
+          <t>-24,05; 24,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,27; -15,01</t>
+          <t>-52,63; -14,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,59; -9,01</t>
+          <t>-81,07; -8,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 73,92</t>
+          <t>-17,97; 74,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 56,69</t>
+          <t>-40,63; 52,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 34,41</t>
+          <t>-34,64; 34,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 30,07</t>
+          <t>-13,16; 30,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,25; -7,34</t>
+          <t>-43,16; -6,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,86; -6,78</t>
+          <t>-73,31; -6,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; -0,14</t>
+          <t>-6,38; 0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -3,69</t>
+          <t>-9,89; -3,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -2,91</t>
+          <t>-9,09; -2,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 7,45</t>
+          <t>-2,01; 7,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,48; -2,48</t>
+          <t>-10,66; -2,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 43,23</t>
+          <t>-5,3; 38,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,96</t>
+          <t>-3,19; 2,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -4,15</t>
+          <t>-8,68; -3,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 27,82</t>
+          <t>-5,62; 28,35</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,06; -0,78</t>
+          <t>-29,82; 0,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,68; -20,21</t>
+          <t>-45,24; -19,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -15,95</t>
+          <t>-42,55; -14,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 35,95</t>
+          <t>-8,14; 34,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -11,54</t>
+          <t>-41,82; -12,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 197,96</t>
+          <t>-22,15; 177,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 9,98</t>
+          <t>-14,44; 10,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,44; -20,72</t>
+          <t>-39,28; -20,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 139,55</t>
+          <t>-25,75; 136,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 0,12</t>
+          <t>-10,05; 0,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -1,07</t>
+          <t>-10,53; -0,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 2,58</t>
+          <t>-8,77; 2,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 7,07</t>
+          <t>-2,44; 7,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 0,89</t>
+          <t>-9,13; 0,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,3; -0,98</t>
+          <t>-11,82; -0,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,96</t>
+          <t>-4,18; 3,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -1,49</t>
+          <t>-8,58; -1,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -1,03</t>
+          <t>-8,81; -0,73</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,42; -0,05</t>
+          <t>-45,19; 3,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -6,74</t>
+          <t>-48,59; -4,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 16,93</t>
+          <t>-39,72; 13,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 31,17</t>
+          <t>-9,08; 35,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 3,82</t>
+          <t>-32,13; 4,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,15; -4,67</t>
+          <t>-42,95; -3,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 14,21</t>
+          <t>-17,02; 15,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,41; -6,93</t>
+          <t>-34,68; -8,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -5,02</t>
+          <t>-35,71; -3,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,63</t>
+          <t>-4,26; 4,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,16</t>
+          <t>-5,28; 3,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 7,65</t>
+          <t>-4,52; 8,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,71</t>
+          <t>1,7; 8,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -2,63</t>
+          <t>-9,9; -3,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -1,28</t>
+          <t>-8,04; -1,61</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,44</t>
+          <t>1,22; 7,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,21; -2,75</t>
+          <t>-8,28; -2,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,97; -0,82</t>
+          <t>-6,83; -0,86</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 84,93</t>
+          <t>-46,2; 86,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-55,22; 60,1</t>
+          <t>-54,07; 63,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 133,13</t>
+          <t>-51,31; 148,44</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,55; 43,5</t>
+          <t>6,91; 43,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-40,84; -12,89</t>
+          <t>-42,78; -16,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-33,96; -6,26</t>
+          <t>-33,37; -8,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,37; 41,9</t>
+          <t>5,86; 41,28</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,17; -15,85</t>
+          <t>-40,72; -15,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-33,7; -4,51</t>
+          <t>-33,42; -4,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,74</t>
+          <t>-3,01; 0,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,11; -3,67</t>
+          <t>-7,03; -3,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -2,55</t>
+          <t>-7,3; -2,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,63</t>
+          <t>1,46; 5,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,69; -3,91</t>
+          <t>-7,59; -3,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 16,23</t>
+          <t>-4,14; 14,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,65</t>
+          <t>-0,09; 2,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,78; -4,19</t>
+          <t>-6,9; -4,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 7,33</t>
+          <t>-4,66; 7,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 4,43</t>
+          <t>-17,06; 4,52</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,11; -22,5</t>
+          <t>-39,69; -22,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,96; -15,36</t>
+          <t>-42,54; -15,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,28; 26,22</t>
+          <t>6,34; 27,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -18,27</t>
+          <t>-32,83; -17,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 72,82</t>
+          <t>-18,13; 63,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 14,04</t>
+          <t>-0,43; 14,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-33,07; -22,01</t>
+          <t>-33,51; -22,21</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 37,03</t>
+          <t>-23,43; 36,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_1_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-2,24</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 7,11</t>
+          <t>-3,24; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; -0,55</t>
+          <t>-9,38; 0,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 2,08</t>
+          <t>-7,09; 1,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 5,16</t>
+          <t>-8,15; 4,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; -2,47</t>
+          <t>-13,78; -2,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 2,14</t>
+          <t>-7,92; 2,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 4,13</t>
+          <t>-3,81; 4,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -2,52</t>
+          <t>-9,78; -2,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 1,43</t>
+          <t>-5,57; 1,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-16,52%</t>
+          <t>-16,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,14%</t>
+          <t>-12,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,36%</t>
+          <t>-13,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 53,64</t>
+          <t>-17,74; 55,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,3; -3,37</t>
+          <t>-52,87; 4,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 16,56</t>
+          <t>-40,85; 13,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 32,85</t>
+          <t>-37,15; 27,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,6; -13,65</t>
+          <t>-59,44; -10,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 15,11</t>
+          <t>-34,83; 18,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 27,21</t>
+          <t>-19,86; 26,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,9; -16,4</t>
+          <t>-50,95; -16,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 10,03</t>
+          <t>-28,61; 11,71</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 9,23</t>
+          <t>-2,13; 8,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 2,44</t>
+          <t>-7,23; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,57</t>
+          <t>-4,44; 4,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 10,65</t>
+          <t>-1,15; 11,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -2,45</t>
+          <t>-13,02; -2,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 5,26</t>
+          <t>-6,85; 4,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,9</t>
+          <t>-0,4; 7,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; -1,44</t>
+          <t>-8,46; -1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,5</t>
+          <t>-4,56; 2,87</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>-0,24%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,15%</t>
+          <t>-3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,2%</t>
+          <t>-4,33%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 101,5</t>
+          <t>-15,95; 87,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 26,96</t>
+          <t>-50,39; 23,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 60,49</t>
+          <t>-29,99; 47,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 57,97</t>
+          <t>-6,54; 63,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -12,23</t>
+          <t>-55,8; -13,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 29,45</t>
+          <t>-27,55; 25,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 55,59</t>
+          <t>-2,52; 53,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,06; -10,83</t>
+          <t>-47,68; -10,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 23,2</t>
+          <t>-24,2; 19,82</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,73</t>
+          <t>-3,6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,4</t>
+          <t>-2,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,93</t>
+          <t>-5,38; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,15; -2,53</t>
+          <t>-11,66; -2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -1,62</t>
+          <t>-8,13; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 12,51</t>
+          <t>-4,41; 12,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 8,83</t>
+          <t>-9,72; 8,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 5,61</t>
+          <t>-9,93; 6,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,19</t>
+          <t>-3,14; 4,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -1,2</t>
+          <t>-9,34; -1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -1,26</t>
+          <t>-6,56; 1,72</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-47,27%</t>
+          <t>-19,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-6,91%</t>
+          <t>-8,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-38,56%</t>
+          <t>-15,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 24,09</t>
+          <t>-25,6; 25,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,63; -14,39</t>
+          <t>-53,85; -15,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,07; -8,58</t>
+          <t>-40,08; 5,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 74,62</t>
+          <t>-19,34; 78,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 52,4</t>
+          <t>-38,93; 50,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 34,68</t>
+          <t>-37,65; 38,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 30,78</t>
+          <t>-14,51; 28,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -6,09</t>
+          <t>-43,86; -7,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,31; -6,54</t>
+          <t>-31,15; 9,53</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-5,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,17</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>-4,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,05</t>
+          <t>-6,59; -0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -3,71</t>
+          <t>-10,01; -4,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,09; -2,78</t>
+          <t>-8,97; -2,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 7,29</t>
+          <t>-1,64; 7,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,66; -2,51</t>
+          <t>-10,61; -2,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 38,94</t>
+          <t>-7,39; 0,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,1</t>
+          <t>-3,33; 1,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -3,91</t>
+          <t>-8,89; -3,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 28,35</t>
+          <t>-6,87; -1,93</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,54%</t>
+          <t>-29,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>-14,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>-21,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 0,28</t>
+          <t>-30,52; 0,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,24; -19,54</t>
+          <t>-45,76; -22,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,55; -14,9</t>
+          <t>-41,38; -14,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 34,56</t>
+          <t>-6,21; 35,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -12,06</t>
+          <t>-41,34; -11,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 177,46</t>
+          <t>-28,76; 0,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 10,53</t>
+          <t>-14,59; 9,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -20,04</t>
+          <t>-39,86; -20,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 136,23</t>
+          <t>-30,59; -9,83</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,25</t>
+          <t>-4,51</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,37</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>-3,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 0,25</t>
+          <t>-9,54; 0,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,53; -0,59</t>
+          <t>-10,8; -0,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 2,11</t>
+          <t>-9,34; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,85</t>
+          <t>-3,03; 7,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 0,82</t>
+          <t>-9,24; 0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -0,68</t>
+          <t>-6,94; 1,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,22</t>
+          <t>-4,49; 3,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -1,77</t>
+          <t>-8,63; -1,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -0,73</t>
+          <t>-6,61; -0,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-17,17%</t>
+          <t>-23,83%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-21,12%</t>
+          <t>-9,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-19,49%</t>
+          <t>-14,97%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 3,06</t>
+          <t>-43,72; 2,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,59; -4,05</t>
+          <t>-48,22; -5,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 13,93</t>
+          <t>-43,12; 5,02</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 35,58</t>
+          <t>-11,0; 34,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 4,48</t>
+          <t>-32,08; 4,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,95; -3,2</t>
+          <t>-24,0; 9,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 15,43</t>
+          <t>-17,95; 14,6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-34,68; -8,15</t>
+          <t>-35,14; -9,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,71; -3,57</t>
+          <t>-26,33; -0,3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,56</t>
+          <t>-5,1</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-4,12</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 4,6</t>
+          <t>-3,9; 4,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,45</t>
+          <t>-5,3; 2,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 8,11</t>
+          <t>-4,18; 7,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,82</t>
+          <t>1,43; 8,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,9; -3,26</t>
+          <t>-9,45; -3,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -1,61</t>
+          <t>-8,27; -1,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,29</t>
+          <t>0,94; 7,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -2,81</t>
+          <t>-8,32; -2,71</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,86</t>
+          <t>-7,01; -1,35</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-20,97%</t>
+          <t>-23,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-20,92%</t>
+          <t>-21,66%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 86,35</t>
+          <t>-41,85; 84,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 63,62</t>
+          <t>-55,06; 52,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 148,44</t>
+          <t>-46,8; 144,0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,91; 43,5</t>
+          <t>5,86; 42,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,78; -16,64</t>
+          <t>-41,04; -15,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-33,37; -8,03</t>
+          <t>-35,16; -8,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,86; 41,28</t>
+          <t>4,83; 40,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,72; -15,44</t>
+          <t>-40,45; -14,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-33,42; -4,49</t>
+          <t>-34,45; -6,62</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>-2,9</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>-3,2</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,73</t>
+          <t>-2,83; 0,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -3,65</t>
+          <t>-6,98; -3,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -2,41</t>
+          <t>-5,35; -1,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,86</t>
+          <t>1,46; 5,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -3,61</t>
+          <t>-7,56; -3,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 14,24</t>
+          <t>-4,6; -1,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,78</t>
+          <t>-0,18; 2,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -4,21</t>
+          <t>-6,75; -4,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,11</t>
+          <t>-4,38; -1,85</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-25,77%</t>
+          <t>-21,12%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>-12,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-7,6%</t>
+          <t>-16,26%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 4,52</t>
+          <t>-15,57; 4,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -22,67</t>
+          <t>-39,01; -21,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,54; -15,02</t>
+          <t>-30,19; -11,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,34; 27,96</t>
+          <t>6,33; 25,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -17,06</t>
+          <t>-32,69; -17,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 63,61</t>
+          <t>-19,64; -5,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 14,65</t>
+          <t>-0,91; 14,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-33,51; -22,21</t>
+          <t>-33,35; -21,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 36,84</t>
+          <t>-21,48; -9,87</t>
         </is>
       </c>
     </row>
